--- a/Ma_Seri.xlsx
+++ b/Ma_Seri.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\group_project\GraduationProject\client\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GROUP-PROJECT\GraduationProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="795">
   <si>
     <t>STT</t>
   </si>
@@ -2406,13 +2406,16 @@
   </si>
   <si>
     <t>WATCH</t>
+  </si>
+  <si>
+    <t>LP-918273644</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2439,6 +2442,19 @@
     <font>
       <b/>
       <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2485,7 +2501,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2497,6 +2513,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2779,7 +2801,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:K102"/>
+  <dimension ref="A2:K103"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.54296875" customWidth="1"/>
@@ -2830,28 +2852,28 @@
       <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="5" t="s">
         <v>676</v>
       </c>
     </row>
@@ -2859,28 +2881,28 @@
       <c r="A4" s="3">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>486</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>388</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>582</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="5" t="s">
         <v>677</v>
       </c>
     </row>
@@ -2888,28 +2910,28 @@
       <c r="A5" s="3">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>487</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>389</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>583</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="5" t="s">
         <v>678</v>
       </c>
     </row>
@@ -2917,28 +2939,28 @@
       <c r="A6" s="3">
         <v>4</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>488</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>584</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="5" t="s">
         <v>679</v>
       </c>
     </row>
@@ -2946,28 +2968,28 @@
       <c r="A7" s="3">
         <v>5</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>489</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="5" t="s">
         <v>585</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="5" t="s">
         <v>680</v>
       </c>
     </row>
@@ -2975,28 +2997,28 @@
       <c r="A8" s="3">
         <v>6</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="5" t="s">
         <v>490</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>586</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="5" t="s">
         <v>681</v>
       </c>
     </row>
@@ -3004,28 +3026,28 @@
       <c r="A9" s="3">
         <v>7</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="5" t="s">
         <v>491</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="5" t="s">
         <v>587</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="5" t="s">
         <v>682</v>
       </c>
     </row>
@@ -3033,28 +3055,28 @@
       <c r="A10" s="3">
         <v>8</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="5" t="s">
         <v>394</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="5" t="s">
         <v>588</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="5" t="s">
         <v>683</v>
       </c>
     </row>
@@ -3062,28 +3084,28 @@
       <c r="A11" s="3">
         <v>9</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="5" t="s">
         <v>493</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="5" t="s">
         <v>395</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="5" t="s">
         <v>589</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="5" t="s">
         <v>684</v>
       </c>
     </row>
@@ -3091,28 +3113,28 @@
       <c r="A12" s="3">
         <v>10</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="5" t="s">
         <v>494</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="5" t="s">
         <v>396</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="5" t="s">
         <v>590</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="5" t="s">
         <v>685</v>
       </c>
     </row>
@@ -3120,28 +3142,28 @@
       <c r="A13" s="3">
         <v>11</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="5" t="s">
         <v>495</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="5" t="s">
         <v>591</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="5" t="s">
         <v>686</v>
       </c>
     </row>
@@ -3149,28 +3171,28 @@
       <c r="A14" s="3">
         <v>12</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="5" t="s">
         <v>496</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="5" t="s">
         <v>592</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="5" t="s">
         <v>687</v>
       </c>
     </row>
@@ -3178,28 +3200,28 @@
       <c r="A15" s="3">
         <v>13</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="5" t="s">
         <v>497</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="5" t="s">
         <v>593</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="5" t="s">
         <v>688</v>
       </c>
     </row>
@@ -3207,28 +3229,28 @@
       <c r="A16" s="3">
         <v>14</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="5" t="s">
         <v>498</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="5" t="s">
         <v>689</v>
       </c>
     </row>
@@ -3236,28 +3258,28 @@
       <c r="A17" s="3">
         <v>15</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="5" t="s">
         <v>499</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="5" t="s">
         <v>401</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H17" s="5" t="s">
         <v>595</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="5" t="s">
         <v>690</v>
       </c>
     </row>
@@ -3265,28 +3287,28 @@
       <c r="A18" s="3">
         <v>16</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="5" t="s">
         <v>500</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="5" t="s">
         <v>596</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" s="5" t="s">
         <v>691</v>
       </c>
     </row>
@@ -3294,28 +3316,28 @@
       <c r="A19" s="3">
         <v>17</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="5" t="s">
         <v>501</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="5" t="s">
         <v>597</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="I19" s="5" t="s">
         <v>692</v>
       </c>
     </row>
@@ -3323,28 +3345,28 @@
       <c r="A20" s="3">
         <v>18</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="5" t="s">
         <v>502</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="5" t="s">
         <v>598</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" s="5" t="s">
         <v>693</v>
       </c>
     </row>
@@ -3352,28 +3374,28 @@
       <c r="A21" s="3">
         <v>19</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="5" t="s">
         <v>503</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" s="5" t="s">
         <v>599</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="I21" s="5" t="s">
         <v>694</v>
       </c>
     </row>
@@ -3381,28 +3403,28 @@
       <c r="A22" s="3">
         <v>20</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="5" t="s">
         <v>504</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H22" s="5" t="s">
         <v>600</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="I22" s="5" t="s">
         <v>695</v>
       </c>
     </row>
@@ -3410,28 +3432,28 @@
       <c r="A23" s="3">
         <v>21</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="5" t="s">
         <v>505</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="5" t="s">
         <v>601</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="5" t="s">
         <v>696</v>
       </c>
     </row>
@@ -3439,28 +3461,28 @@
       <c r="A24" s="3">
         <v>22</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="5" t="s">
         <v>506</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="5" t="s">
         <v>408</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="H24" s="5" t="s">
         <v>602</v>
       </c>
-      <c r="I24" s="4" t="s">
+      <c r="I24" s="5" t="s">
         <v>697</v>
       </c>
     </row>
@@ -3468,28 +3490,28 @@
       <c r="A25" s="3">
         <v>23</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="5" t="s">
         <v>507</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="H25" s="4" t="s">
+      <c r="H25" s="5" t="s">
         <v>603</v>
       </c>
-      <c r="I25" s="4" t="s">
+      <c r="I25" s="5" t="s">
         <v>698</v>
       </c>
     </row>
@@ -3497,28 +3519,28 @@
       <c r="A26" s="3">
         <v>24</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="5" t="s">
         <v>508</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="5" t="s">
         <v>410</v>
       </c>
-      <c r="H26" s="4" t="s">
+      <c r="H26" s="5" t="s">
         <v>604</v>
       </c>
-      <c r="I26" s="4" t="s">
+      <c r="I26" s="5" t="s">
         <v>699</v>
       </c>
     </row>
@@ -3526,28 +3548,28 @@
       <c r="A27" s="3">
         <v>25</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="F27" s="5" t="s">
         <v>509</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="H27" s="5" t="s">
         <v>605</v>
       </c>
-      <c r="I27" s="4" t="s">
+      <c r="I27" s="5" t="s">
         <v>700</v>
       </c>
     </row>
@@ -3555,28 +3577,28 @@
       <c r="A28" s="3">
         <v>26</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="5" t="s">
         <v>510</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="5" t="s">
         <v>412</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H28" s="5" t="s">
         <v>606</v>
       </c>
-      <c r="I28" s="4" t="s">
+      <c r="I28" s="5" t="s">
         <v>701</v>
       </c>
     </row>
@@ -3584,28 +3606,28 @@
       <c r="A29" s="3">
         <v>27</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F29" s="5" t="s">
         <v>511</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="H29" s="4" t="s">
+      <c r="H29" s="5" t="s">
         <v>607</v>
       </c>
-      <c r="I29" s="4" t="s">
+      <c r="I29" s="5" t="s">
         <v>702</v>
       </c>
     </row>
@@ -3613,28 +3635,28 @@
       <c r="A30" s="3">
         <v>28</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="F30" s="5" t="s">
         <v>512</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" s="5" t="s">
         <v>414</v>
       </c>
-      <c r="H30" s="4" t="s">
+      <c r="H30" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="I30" s="4" t="s">
+      <c r="I30" s="5" t="s">
         <v>703</v>
       </c>
     </row>
@@ -3642,28 +3664,28 @@
       <c r="A31" s="3">
         <v>29</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="F31" s="5" t="s">
         <v>513</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="5" t="s">
         <v>415</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="H31" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="I31" s="4" t="s">
+      <c r="I31" s="5" t="s">
         <v>704</v>
       </c>
     </row>
@@ -3671,28 +3693,28 @@
       <c r="A32" s="3">
         <v>30</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="5" t="s">
         <v>514</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" s="5" t="s">
         <v>416</v>
       </c>
-      <c r="H32" s="4" t="s">
+      <c r="H32" s="5" t="s">
         <v>610</v>
       </c>
-      <c r="I32" s="4" t="s">
+      <c r="I32" s="5" t="s">
         <v>705</v>
       </c>
     </row>
@@ -3700,28 +3722,28 @@
       <c r="A33" s="3">
         <v>31</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="5" t="s">
         <v>224</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F33" s="5" t="s">
         <v>515</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="G33" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="H33" s="4" t="s">
+      <c r="H33" s="5" t="s">
         <v>611</v>
       </c>
-      <c r="I33" s="4" t="s">
+      <c r="I33" s="5" t="s">
         <v>706</v>
       </c>
     </row>
@@ -3729,28 +3751,28 @@
       <c r="A34" s="3">
         <v>32</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="5" t="s">
         <v>225</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="5" t="s">
         <v>516</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="G34" s="5" t="s">
         <v>418</v>
       </c>
-      <c r="H34" s="4" t="s">
+      <c r="H34" s="5" t="s">
         <v>612</v>
       </c>
-      <c r="I34" s="4" t="s">
+      <c r="I34" s="5" t="s">
         <v>707</v>
       </c>
     </row>
@@ -3758,28 +3780,28 @@
       <c r="A35" s="3">
         <v>33</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="5" t="s">
         <v>226</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="F35" s="5" t="s">
         <v>517</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G35" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="H35" s="4" t="s">
+      <c r="H35" s="5" t="s">
         <v>613</v>
       </c>
-      <c r="I35" s="4" t="s">
+      <c r="I35" s="5" t="s">
         <v>708</v>
       </c>
     </row>
@@ -3787,28 +3809,28 @@
       <c r="A36" s="3">
         <v>34</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="5" t="s">
         <v>227</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="5" t="s">
         <v>518</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G36" s="5" t="s">
         <v>420</v>
       </c>
-      <c r="H36" s="4" t="s">
+      <c r="H36" s="5" t="s">
         <v>614</v>
       </c>
-      <c r="I36" s="4" t="s">
+      <c r="I36" s="5" t="s">
         <v>709</v>
       </c>
     </row>
@@ -3816,28 +3838,28 @@
       <c r="A37" s="3">
         <v>35</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="5" t="s">
         <v>228</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F37" s="5" t="s">
         <v>519</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="G37" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="H37" s="4" t="s">
+      <c r="H37" s="5" t="s">
         <v>615</v>
       </c>
-      <c r="I37" s="4" t="s">
+      <c r="I37" s="5" t="s">
         <v>710</v>
       </c>
     </row>
@@ -3845,28 +3867,28 @@
       <c r="A38" s="3">
         <v>36</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="5" t="s">
         <v>229</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F38" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="G38" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="H38" s="4" t="s">
+      <c r="H38" s="5" t="s">
         <v>616</v>
       </c>
-      <c r="I38" s="4" t="s">
+      <c r="I38" s="5" t="s">
         <v>711</v>
       </c>
     </row>
@@ -3874,28 +3896,28 @@
       <c r="A39" s="3">
         <v>37</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="5" t="s">
         <v>230</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="F39" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="G39" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="H39" s="4" t="s">
+      <c r="H39" s="5" t="s">
         <v>617</v>
       </c>
-      <c r="I39" s="4" t="s">
+      <c r="I39" s="5" t="s">
         <v>712</v>
       </c>
     </row>
@@ -3903,28 +3925,28 @@
       <c r="A40" s="3">
         <v>38</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="5" t="s">
         <v>231</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="F40" s="5" t="s">
         <v>522</v>
       </c>
-      <c r="G40" s="4" t="s">
+      <c r="G40" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="H40" s="4" t="s">
+      <c r="H40" s="5" t="s">
         <v>618</v>
       </c>
-      <c r="I40" s="4" t="s">
+      <c r="I40" s="5" t="s">
         <v>713</v>
       </c>
     </row>
@@ -3932,28 +3954,28 @@
       <c r="A41" s="3">
         <v>39</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="5" t="s">
         <v>232</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="F41" s="4" t="s">
+      <c r="F41" s="5" t="s">
         <v>523</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="G41" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="H41" s="4" t="s">
+      <c r="H41" s="5" t="s">
         <v>619</v>
       </c>
-      <c r="I41" s="4" t="s">
+      <c r="I41" s="5" t="s">
         <v>714</v>
       </c>
     </row>
@@ -3961,28 +3983,28 @@
       <c r="A42" s="3">
         <v>40</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="5" t="s">
         <v>233</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="F42" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="G42" s="5" t="s">
         <v>426</v>
       </c>
-      <c r="H42" s="4" t="s">
+      <c r="H42" s="5" t="s">
         <v>620</v>
       </c>
-      <c r="I42" s="4" t="s">
+      <c r="I42" s="5" t="s">
         <v>715</v>
       </c>
     </row>
@@ -3990,7 +4012,7 @@
       <c r="A43" s="3">
         <v>41</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C43" s="4" t="s">
@@ -4002,16 +4024,16 @@
       <c r="E43" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F43" s="5" t="s">
         <v>525</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="G43" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="H43" s="4" t="s">
+      <c r="H43" s="5" t="s">
         <v>621</v>
       </c>
-      <c r="I43" s="4" t="s">
+      <c r="I43" s="5" t="s">
         <v>716</v>
       </c>
     </row>
@@ -4019,7 +4041,7 @@
       <c r="A44" s="3">
         <v>42</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="5" t="s">
         <v>42</v>
       </c>
       <c r="C44" s="4" t="s">
@@ -4031,16 +4053,16 @@
       <c r="E44" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F44" s="5" t="s">
         <v>526</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="G44" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="H44" s="4" t="s">
+      <c r="H44" s="5" t="s">
         <v>622</v>
       </c>
-      <c r="I44" s="4" t="s">
+      <c r="I44" s="5" t="s">
         <v>717</v>
       </c>
     </row>
@@ -4048,7 +4070,7 @@
       <c r="A45" s="3">
         <v>43</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C45" s="4" t="s">
@@ -4060,16 +4082,16 @@
       <c r="E45" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="F45" s="5" t="s">
         <v>527</v>
       </c>
-      <c r="G45" s="4" t="s">
+      <c r="G45" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="H45" s="4" t="s">
+      <c r="H45" s="5" t="s">
         <v>623</v>
       </c>
-      <c r="I45" s="4" t="s">
+      <c r="I45" s="5" t="s">
         <v>718</v>
       </c>
     </row>
@@ -4077,7 +4099,7 @@
       <c r="A46" s="3">
         <v>44</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C46" s="4" t="s">
@@ -4089,16 +4111,16 @@
       <c r="E46" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="F46" s="5" t="s">
         <v>528</v>
       </c>
-      <c r="G46" s="4" t="s">
+      <c r="G46" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="H46" s="4" t="s">
+      <c r="H46" s="5" t="s">
         <v>624</v>
       </c>
-      <c r="I46" s="4" t="s">
+      <c r="I46" s="5" t="s">
         <v>719</v>
       </c>
     </row>
@@ -4106,7 +4128,7 @@
       <c r="A47" s="3">
         <v>45</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C47" s="4" t="s">
@@ -4118,16 +4140,16 @@
       <c r="E47" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="F47" s="5" t="s">
         <v>529</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="G47" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="H47" s="4" t="s">
+      <c r="H47" s="5" t="s">
         <v>625</v>
       </c>
-      <c r="I47" s="4" t="s">
+      <c r="I47" s="5" t="s">
         <v>720</v>
       </c>
     </row>
@@ -4135,7 +4157,7 @@
       <c r="A48" s="3">
         <v>46</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C48" s="4" t="s">
@@ -4147,16 +4169,16 @@
       <c r="E48" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="F48" s="5" t="s">
         <v>530</v>
       </c>
-      <c r="G48" s="4" t="s">
+      <c r="G48" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="H48" s="4" t="s">
+      <c r="H48" s="5" t="s">
         <v>626</v>
       </c>
-      <c r="I48" s="4" t="s">
+      <c r="I48" s="5" t="s">
         <v>721</v>
       </c>
     </row>
@@ -4164,7 +4186,7 @@
       <c r="A49" s="3">
         <v>47</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="5" t="s">
         <v>47</v>
       </c>
       <c r="C49" s="4" t="s">
@@ -4176,16 +4198,16 @@
       <c r="E49" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="F49" s="4" t="s">
+      <c r="F49" s="5" t="s">
         <v>531</v>
       </c>
-      <c r="G49" s="4" t="s">
+      <c r="G49" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="H49" s="4" t="s">
+      <c r="H49" s="5" t="s">
         <v>627</v>
       </c>
-      <c r="I49" s="4" t="s">
+      <c r="I49" s="5" t="s">
         <v>722</v>
       </c>
     </row>
@@ -4193,7 +4215,7 @@
       <c r="A50" s="3">
         <v>48</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="5" t="s">
         <v>48</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -4205,16 +4227,16 @@
       <c r="E50" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="F50" s="4" t="s">
+      <c r="F50" s="5" t="s">
         <v>532</v>
       </c>
-      <c r="G50" s="4" t="s">
+      <c r="G50" s="5" t="s">
         <v>434</v>
       </c>
-      <c r="H50" s="4" t="s">
+      <c r="H50" s="5" t="s">
         <v>628</v>
       </c>
-      <c r="I50" s="4" t="s">
+      <c r="I50" s="5" t="s">
         <v>723</v>
       </c>
     </row>
@@ -4222,7 +4244,7 @@
       <c r="A51" s="3">
         <v>49</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C51" s="4" t="s">
@@ -4234,16 +4256,16 @@
       <c r="E51" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="F51" s="4" t="s">
+      <c r="F51" s="5" t="s">
         <v>533</v>
       </c>
-      <c r="G51" s="4" t="s">
+      <c r="G51" s="5" t="s">
         <v>435</v>
       </c>
-      <c r="H51" s="4" t="s">
+      <c r="H51" s="5" t="s">
         <v>629</v>
       </c>
-      <c r="I51" s="4" t="s">
+      <c r="I51" s="5" t="s">
         <v>724</v>
       </c>
     </row>
@@ -4251,7 +4273,7 @@
       <c r="A52" s="3">
         <v>50</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C52" s="4" t="s">
@@ -4263,16 +4285,16 @@
       <c r="E52" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="F52" s="4" t="s">
+      <c r="F52" s="5" t="s">
         <v>534</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="G52" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="H52" s="4" t="s">
+      <c r="H52" s="5" t="s">
         <v>630</v>
       </c>
-      <c r="I52" s="4" t="s">
+      <c r="I52" s="5" t="s">
         <v>725</v>
       </c>
     </row>
@@ -4280,7 +4302,7 @@
       <c r="A53" s="3">
         <v>51</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="5" t="s">
         <v>51</v>
       </c>
       <c r="C53" s="4" t="s">
@@ -4292,16 +4314,16 @@
       <c r="E53" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="F53" s="4" t="s">
+      <c r="F53" s="5" t="s">
         <v>535</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="H53" s="4" t="s">
+      <c r="H53" s="5" t="s">
         <v>631</v>
       </c>
-      <c r="I53" s="4" t="s">
+      <c r="I53" s="5" t="s">
         <v>726</v>
       </c>
     </row>
@@ -4309,7 +4331,7 @@
       <c r="A54" s="3">
         <v>52</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="5" t="s">
         <v>52</v>
       </c>
       <c r="C54" s="4" t="s">
@@ -4321,16 +4343,16 @@
       <c r="E54" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="F54" s="5" t="s">
         <v>536</v>
       </c>
       <c r="G54" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="H54" s="4" t="s">
+      <c r="H54" s="5" t="s">
         <v>632</v>
       </c>
-      <c r="I54" s="4" t="s">
+      <c r="I54" s="5" t="s">
         <v>727</v>
       </c>
     </row>
@@ -4338,7 +4360,7 @@
       <c r="A55" s="3">
         <v>53</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C55" s="4" t="s">
@@ -4350,16 +4372,16 @@
       <c r="E55" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="F55" s="4" t="s">
+      <c r="F55" s="5" t="s">
         <v>537</v>
       </c>
       <c r="G55" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="H55" s="4" t="s">
+      <c r="H55" s="5" t="s">
         <v>633</v>
       </c>
-      <c r="I55" s="4" t="s">
+      <c r="I55" s="5" t="s">
         <v>728</v>
       </c>
     </row>
@@ -4367,7 +4389,7 @@
       <c r="A56" s="3">
         <v>54</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="5" t="s">
         <v>54</v>
       </c>
       <c r="C56" s="4" t="s">
@@ -4379,16 +4401,16 @@
       <c r="E56" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="F56" s="4" t="s">
+      <c r="F56" s="5" t="s">
         <v>538</v>
       </c>
       <c r="G56" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="H56" s="4" t="s">
+      <c r="H56" s="5" t="s">
         <v>634</v>
       </c>
-      <c r="I56" s="4" t="s">
+      <c r="I56" s="5" t="s">
         <v>729</v>
       </c>
     </row>
@@ -4396,7 +4418,7 @@
       <c r="A57" s="3">
         <v>55</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="5" t="s">
         <v>55</v>
       </c>
       <c r="C57" s="4" t="s">
@@ -4408,16 +4430,16 @@
       <c r="E57" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="F57" s="4" t="s">
+      <c r="F57" s="5" t="s">
         <v>539</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="H57" s="4" t="s">
+      <c r="H57" s="5" t="s">
         <v>635</v>
       </c>
-      <c r="I57" s="4" t="s">
+      <c r="I57" s="5" t="s">
         <v>730</v>
       </c>
     </row>
@@ -4425,7 +4447,7 @@
       <c r="A58" s="3">
         <v>56</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C58" s="4" t="s">
@@ -4437,16 +4459,16 @@
       <c r="E58" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="F58" s="4" t="s">
+      <c r="F58" s="5" t="s">
         <v>540</v>
       </c>
       <c r="G58" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="H58" s="4" t="s">
+      <c r="H58" s="5" t="s">
         <v>636</v>
       </c>
-      <c r="I58" s="4" t="s">
+      <c r="I58" s="5" t="s">
         <v>731</v>
       </c>
     </row>
@@ -4454,7 +4476,7 @@
       <c r="A59" s="3">
         <v>57</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="5" t="s">
         <v>57</v>
       </c>
       <c r="C59" s="4" t="s">
@@ -4466,16 +4488,16 @@
       <c r="E59" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="F59" s="4" t="s">
+      <c r="F59" s="5" t="s">
         <v>541</v>
       </c>
       <c r="G59" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="H59" s="4" t="s">
+      <c r="H59" s="5" t="s">
         <v>637</v>
       </c>
-      <c r="I59" s="4" t="s">
+      <c r="I59" s="5" t="s">
         <v>732</v>
       </c>
     </row>
@@ -4483,7 +4505,7 @@
       <c r="A60" s="3">
         <v>58</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="5" t="s">
         <v>58</v>
       </c>
       <c r="C60" s="4" t="s">
@@ -4495,16 +4517,16 @@
       <c r="E60" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="F60" s="4" t="s">
+      <c r="F60" s="5" t="s">
         <v>542</v>
       </c>
       <c r="G60" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="H60" s="4" t="s">
+      <c r="H60" s="5" t="s">
         <v>638</v>
       </c>
-      <c r="I60" s="4" t="s">
+      <c r="I60" s="5" t="s">
         <v>733</v>
       </c>
     </row>
@@ -4512,7 +4534,7 @@
       <c r="A61" s="3">
         <v>59</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C61" s="4" t="s">
@@ -4524,16 +4546,16 @@
       <c r="E61" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="F61" s="4" t="s">
+      <c r="F61" s="5" t="s">
         <v>543</v>
       </c>
       <c r="G61" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="H61" s="4" t="s">
+      <c r="H61" s="5" t="s">
         <v>639</v>
       </c>
-      <c r="I61" s="4" t="s">
+      <c r="I61" s="5" t="s">
         <v>734</v>
       </c>
     </row>
@@ -4541,7 +4563,7 @@
       <c r="A62" s="3">
         <v>60</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="5" t="s">
         <v>60</v>
       </c>
       <c r="C62" s="4" t="s">
@@ -4553,16 +4575,16 @@
       <c r="E62" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="F62" s="4" t="s">
+      <c r="F62" s="5" t="s">
         <v>544</v>
       </c>
       <c r="G62" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="H62" s="4" t="s">
+      <c r="H62" s="5" t="s">
         <v>640</v>
       </c>
-      <c r="I62" s="4" t="s">
+      <c r="I62" s="5" t="s">
         <v>735</v>
       </c>
     </row>
@@ -4570,7 +4592,7 @@
       <c r="A63" s="3">
         <v>61</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="5" t="s">
         <v>61</v>
       </c>
       <c r="C63" s="4" t="s">
@@ -4582,16 +4604,16 @@
       <c r="E63" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="F63" s="4" t="s">
+      <c r="F63" s="5" t="s">
         <v>545</v>
       </c>
       <c r="G63" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="H63" s="4" t="s">
+      <c r="H63" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="I63" s="4" t="s">
+      <c r="I63" s="5" t="s">
         <v>736</v>
       </c>
     </row>
@@ -4599,7 +4621,7 @@
       <c r="A64" s="3">
         <v>62</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="5" t="s">
         <v>62</v>
       </c>
       <c r="C64" s="4" t="s">
@@ -4611,16 +4633,16 @@
       <c r="E64" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="F64" s="4" t="s">
+      <c r="F64" s="5" t="s">
         <v>546</v>
       </c>
       <c r="G64" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="H64" s="4" t="s">
+      <c r="H64" s="5" t="s">
         <v>642</v>
       </c>
-      <c r="I64" s="4" t="s">
+      <c r="I64" s="5" t="s">
         <v>737</v>
       </c>
     </row>
@@ -4628,7 +4650,7 @@
       <c r="A65" s="3">
         <v>63</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B65" s="5" t="s">
         <v>63</v>
       </c>
       <c r="C65" s="4" t="s">
@@ -4640,16 +4662,16 @@
       <c r="E65" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="F65" s="4" t="s">
+      <c r="F65" s="5" t="s">
         <v>547</v>
       </c>
       <c r="G65" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="H65" s="4" t="s">
+      <c r="H65" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="I65" s="4" t="s">
+      <c r="I65" s="5" t="s">
         <v>738</v>
       </c>
     </row>
@@ -4657,7 +4679,7 @@
       <c r="A66" s="3">
         <v>64</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="5" t="s">
         <v>64</v>
       </c>
       <c r="C66" s="4" t="s">
@@ -4669,16 +4691,16 @@
       <c r="E66" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="F66" s="4" t="s">
+      <c r="F66" s="5" t="s">
         <v>548</v>
       </c>
       <c r="G66" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="H66" s="4" t="s">
+      <c r="H66" s="5" t="s">
         <v>644</v>
       </c>
-      <c r="I66" s="4" t="s">
+      <c r="I66" s="5" t="s">
         <v>739</v>
       </c>
     </row>
@@ -4686,7 +4708,7 @@
       <c r="A67" s="3">
         <v>65</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B67" s="5" t="s">
         <v>65</v>
       </c>
       <c r="C67" s="4" t="s">
@@ -4698,16 +4720,16 @@
       <c r="E67" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="F67" s="4" t="s">
+      <c r="F67" s="5" t="s">
         <v>549</v>
       </c>
       <c r="G67" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="H67" s="4" t="s">
+      <c r="H67" s="5" t="s">
         <v>645</v>
       </c>
-      <c r="I67" s="4" t="s">
+      <c r="I67" s="5" t="s">
         <v>740</v>
       </c>
     </row>
@@ -4715,7 +4737,7 @@
       <c r="A68" s="3">
         <v>66</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="5" t="s">
         <v>66</v>
       </c>
       <c r="C68" s="4" t="s">
@@ -4727,16 +4749,16 @@
       <c r="E68" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="F68" s="4" t="s">
-        <v>487</v>
+      <c r="F68" s="5" t="s">
+        <v>794</v>
       </c>
       <c r="G68" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="H68" s="4" t="s">
+      <c r="H68" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="I68" s="4" t="s">
+      <c r="I68" s="5" t="s">
         <v>741</v>
       </c>
     </row>
@@ -4744,7 +4766,7 @@
       <c r="A69" s="3">
         <v>67</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B69" s="5" t="s">
         <v>67</v>
       </c>
       <c r="C69" s="4" t="s">
@@ -4756,16 +4778,16 @@
       <c r="E69" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="F69" s="4" t="s">
+      <c r="F69" s="5" t="s">
         <v>550</v>
       </c>
       <c r="G69" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="H69" s="4" t="s">
+      <c r="H69" s="5" t="s">
         <v>647</v>
       </c>
-      <c r="I69" s="4" t="s">
+      <c r="I69" s="5" t="s">
         <v>742</v>
       </c>
     </row>
@@ -4773,7 +4795,7 @@
       <c r="A70" s="3">
         <v>68</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B70" s="5" t="s">
         <v>68</v>
       </c>
       <c r="C70" s="4" t="s">
@@ -4785,16 +4807,16 @@
       <c r="E70" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="F70" s="4" t="s">
+      <c r="F70" s="5" t="s">
         <v>551</v>
       </c>
       <c r="G70" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="H70" s="4" t="s">
+      <c r="H70" s="5" t="s">
         <v>648</v>
       </c>
-      <c r="I70" s="4" t="s">
+      <c r="I70" s="5" t="s">
         <v>743</v>
       </c>
     </row>
@@ -4802,7 +4824,7 @@
       <c r="A71" s="3">
         <v>69</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B71" s="5" t="s">
         <v>69</v>
       </c>
       <c r="C71" s="4" t="s">
@@ -4814,16 +4836,16 @@
       <c r="E71" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="F71" s="4" t="s">
+      <c r="F71" s="5" t="s">
         <v>552</v>
       </c>
       <c r="G71" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="H71" s="4" t="s">
+      <c r="H71" s="5" t="s">
         <v>649</v>
       </c>
-      <c r="I71" s="4" t="s">
+      <c r="I71" s="5" t="s">
         <v>744</v>
       </c>
     </row>
@@ -4831,7 +4853,7 @@
       <c r="A72" s="3">
         <v>70</v>
       </c>
-      <c r="B72" s="4" t="s">
+      <c r="B72" s="5" t="s">
         <v>70</v>
       </c>
       <c r="C72" s="4" t="s">
@@ -4843,16 +4865,16 @@
       <c r="E72" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="F72" s="4" t="s">
+      <c r="F72" s="5" t="s">
         <v>553</v>
       </c>
       <c r="G72" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="H72" s="4" t="s">
+      <c r="H72" s="5" t="s">
         <v>650</v>
       </c>
-      <c r="I72" s="4" t="s">
+      <c r="I72" s="5" t="s">
         <v>745</v>
       </c>
     </row>
@@ -4860,7 +4882,7 @@
       <c r="A73" s="3">
         <v>71</v>
       </c>
-      <c r="B73" s="4" t="s">
+      <c r="B73" s="5" t="s">
         <v>71</v>
       </c>
       <c r="C73" s="4" t="s">
@@ -4878,10 +4900,10 @@
       <c r="G73" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="H73" s="4" t="s">
+      <c r="H73" s="5" t="s">
         <v>651</v>
       </c>
-      <c r="I73" s="4" t="s">
+      <c r="I73" s="5" t="s">
         <v>746</v>
       </c>
     </row>
@@ -4889,7 +4911,7 @@
       <c r="A74" s="3">
         <v>72</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="5" t="s">
         <v>72</v>
       </c>
       <c r="C74" s="4" t="s">
@@ -4907,10 +4929,10 @@
       <c r="G74" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="H74" s="4" t="s">
+      <c r="H74" s="5" t="s">
         <v>652</v>
       </c>
-      <c r="I74" s="4" t="s">
+      <c r="I74" s="5" t="s">
         <v>747</v>
       </c>
     </row>
@@ -4918,7 +4940,7 @@
       <c r="A75" s="3">
         <v>73</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="B75" s="5" t="s">
         <v>73</v>
       </c>
       <c r="C75" s="4" t="s">
@@ -4936,10 +4958,10 @@
       <c r="G75" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="H75" s="4" t="s">
+      <c r="H75" s="5" t="s">
         <v>653</v>
       </c>
-      <c r="I75" s="4" t="s">
+      <c r="I75" s="5" t="s">
         <v>748</v>
       </c>
     </row>
@@ -4947,7 +4969,7 @@
       <c r="A76" s="3">
         <v>74</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="5" t="s">
         <v>74</v>
       </c>
       <c r="C76" s="4" t="s">
@@ -4965,10 +4987,10 @@
       <c r="G76" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="H76" s="4" t="s">
+      <c r="H76" s="5" t="s">
         <v>588</v>
       </c>
-      <c r="I76" s="4" t="s">
+      <c r="I76" s="5" t="s">
         <v>770</v>
       </c>
     </row>
@@ -4976,7 +4998,7 @@
       <c r="A77" s="3">
         <v>75</v>
       </c>
-      <c r="B77" s="4" t="s">
+      <c r="B77" s="5" t="s">
         <v>75</v>
       </c>
       <c r="C77" s="4" t="s">
@@ -4994,10 +5016,10 @@
       <c r="G77" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="H77" s="4" t="s">
+      <c r="H77" s="5" t="s">
         <v>654</v>
       </c>
-      <c r="I77" s="4" t="s">
+      <c r="I77" s="5" t="s">
         <v>749</v>
       </c>
     </row>
@@ -5005,7 +5027,7 @@
       <c r="A78" s="3">
         <v>76</v>
       </c>
-      <c r="B78" s="4" t="s">
+      <c r="B78" s="5" t="s">
         <v>76</v>
       </c>
       <c r="C78" s="4" t="s">
@@ -5023,7 +5045,7 @@
       <c r="G78" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="H78" s="4" t="s">
+      <c r="H78" s="5" t="s">
         <v>655</v>
       </c>
       <c r="I78" s="4" t="s">
@@ -5034,7 +5056,7 @@
       <c r="A79" s="3">
         <v>77</v>
       </c>
-      <c r="B79" s="4" t="s">
+      <c r="B79" s="5" t="s">
         <v>77</v>
       </c>
       <c r="C79" s="4" t="s">
@@ -5052,7 +5074,7 @@
       <c r="G79" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="H79" s="4" t="s">
+      <c r="H79" s="5" t="s">
         <v>656</v>
       </c>
       <c r="I79" s="4" t="s">
@@ -5063,7 +5085,7 @@
       <c r="A80" s="3">
         <v>78</v>
       </c>
-      <c r="B80" s="4" t="s">
+      <c r="B80" s="5" t="s">
         <v>78</v>
       </c>
       <c r="C80" s="4" t="s">
@@ -5081,7 +5103,7 @@
       <c r="G80" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="H80" s="4" t="s">
+      <c r="H80" s="5" t="s">
         <v>657</v>
       </c>
       <c r="I80" s="4" t="s">
@@ -5092,7 +5114,7 @@
       <c r="A81" s="3">
         <v>79</v>
       </c>
-      <c r="B81" s="4" t="s">
+      <c r="B81" s="5" t="s">
         <v>79</v>
       </c>
       <c r="C81" s="4" t="s">
@@ -5110,7 +5132,7 @@
       <c r="G81" s="4" t="s">
         <v>465</v>
       </c>
-      <c r="H81" s="4" t="s">
+      <c r="H81" s="5" t="s">
         <v>658</v>
       </c>
       <c r="I81" s="4" t="s">
@@ -5121,7 +5143,7 @@
       <c r="A82" s="3">
         <v>80</v>
       </c>
-      <c r="B82" s="4" t="s">
+      <c r="B82" s="5" t="s">
         <v>80</v>
       </c>
       <c r="C82" s="4" t="s">
@@ -5139,7 +5161,7 @@
       <c r="G82" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="H82" s="4" t="s">
+      <c r="H82" s="5" t="s">
         <v>659</v>
       </c>
       <c r="I82" s="4" t="s">
@@ -5150,7 +5172,7 @@
       <c r="A83" s="3">
         <v>81</v>
       </c>
-      <c r="B83" s="4" t="s">
+      <c r="B83" s="5" t="s">
         <v>81</v>
       </c>
       <c r="C83" s="4" t="s">
@@ -5168,7 +5190,7 @@
       <c r="G83" s="4" t="s">
         <v>467</v>
       </c>
-      <c r="H83" s="4" t="s">
+      <c r="H83" s="5" t="s">
         <v>660</v>
       </c>
       <c r="I83" s="4" t="s">
@@ -5179,7 +5201,7 @@
       <c r="A84" s="3">
         <v>82</v>
       </c>
-      <c r="B84" s="4" t="s">
+      <c r="B84" s="5" t="s">
         <v>82</v>
       </c>
       <c r="C84" s="4" t="s">
@@ -5197,7 +5219,7 @@
       <c r="G84" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="H84" s="4" t="s">
+      <c r="H84" s="5" t="s">
         <v>661</v>
       </c>
       <c r="I84" s="4" t="s">
@@ -5208,7 +5230,7 @@
       <c r="A85" s="3">
         <v>83</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B85" s="5" t="s">
         <v>83</v>
       </c>
       <c r="C85" s="4" t="s">
@@ -5226,7 +5248,7 @@
       <c r="G85" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="H85" s="4" t="s">
+      <c r="H85" s="5" t="s">
         <v>662</v>
       </c>
       <c r="I85" s="4" t="s">
@@ -5237,7 +5259,7 @@
       <c r="A86" s="3">
         <v>84</v>
       </c>
-      <c r="B86" s="4" t="s">
+      <c r="B86" s="5" t="s">
         <v>84</v>
       </c>
       <c r="C86" s="4" t="s">
@@ -5255,7 +5277,7 @@
       <c r="G86" s="4" t="s">
         <v>470</v>
       </c>
-      <c r="H86" s="4" t="s">
+      <c r="H86" s="5" t="s">
         <v>663</v>
       </c>
       <c r="I86" s="4" t="s">
@@ -5266,7 +5288,7 @@
       <c r="A87" s="3">
         <v>85</v>
       </c>
-      <c r="B87" s="4" t="s">
+      <c r="B87" s="5" t="s">
         <v>85</v>
       </c>
       <c r="C87" s="4" t="s">
@@ -5284,7 +5306,7 @@
       <c r="G87" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="H87" s="4" t="s">
+      <c r="H87" s="5" t="s">
         <v>664</v>
       </c>
       <c r="I87" s="4" t="s">
@@ -5295,7 +5317,7 @@
       <c r="A88" s="3">
         <v>86</v>
       </c>
-      <c r="B88" s="4" t="s">
+      <c r="B88" s="5" t="s">
         <v>86</v>
       </c>
       <c r="C88" s="4" t="s">
@@ -5313,7 +5335,7 @@
       <c r="G88" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="H88" s="4" t="s">
+      <c r="H88" s="5" t="s">
         <v>589</v>
       </c>
       <c r="I88" s="4" t="s">
@@ -5324,7 +5346,7 @@
       <c r="A89" s="3">
         <v>87</v>
       </c>
-      <c r="B89" s="4" t="s">
+      <c r="B89" s="5" t="s">
         <v>87</v>
       </c>
       <c r="C89" s="4" t="s">
@@ -5342,7 +5364,7 @@
       <c r="G89" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="H89" s="4" t="s">
+      <c r="H89" s="5" t="s">
         <v>665</v>
       </c>
       <c r="I89" s="4" t="s">
@@ -5353,7 +5375,7 @@
       <c r="A90" s="3">
         <v>88</v>
       </c>
-      <c r="B90" s="4" t="s">
+      <c r="B90" s="5" t="s">
         <v>88</v>
       </c>
       <c r="C90" s="4" t="s">
@@ -5371,7 +5393,7 @@
       <c r="G90" s="4" t="s">
         <v>474</v>
       </c>
-      <c r="H90" s="4" t="s">
+      <c r="H90" s="5" t="s">
         <v>666</v>
       </c>
       <c r="I90" s="4" t="s">
@@ -5382,7 +5404,7 @@
       <c r="A91" s="3">
         <v>89</v>
       </c>
-      <c r="B91" s="4" t="s">
+      <c r="B91" s="5" t="s">
         <v>89</v>
       </c>
       <c r="C91" s="4" t="s">
@@ -5400,7 +5422,7 @@
       <c r="G91" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="H91" s="4" t="s">
+      <c r="H91" s="5" t="s">
         <v>667</v>
       </c>
       <c r="I91" s="4" t="s">
@@ -5411,7 +5433,7 @@
       <c r="A92" s="3">
         <v>90</v>
       </c>
-      <c r="B92" s="4" t="s">
+      <c r="B92" s="5" t="s">
         <v>90</v>
       </c>
       <c r="C92" s="4" t="s">
@@ -5429,7 +5451,7 @@
       <c r="G92" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="H92" s="4" t="s">
+      <c r="H92" s="5" t="s">
         <v>668</v>
       </c>
       <c r="I92" s="4" t="s">
@@ -5440,7 +5462,7 @@
       <c r="A93" s="3">
         <v>91</v>
       </c>
-      <c r="B93" s="4" t="s">
+      <c r="B93" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C93" s="4" t="s">
@@ -5458,7 +5480,7 @@
       <c r="G93" s="4" t="s">
         <v>477</v>
       </c>
-      <c r="H93" s="4" t="s">
+      <c r="H93" s="5" t="s">
         <v>669</v>
       </c>
       <c r="I93" s="4" t="s">
@@ -5469,7 +5491,7 @@
       <c r="A94" s="3">
         <v>92</v>
       </c>
-      <c r="B94" s="4" t="s">
+      <c r="B94" s="5" t="s">
         <v>92</v>
       </c>
       <c r="C94" s="4" t="s">
@@ -5487,7 +5509,7 @@
       <c r="G94" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="H94" s="4" t="s">
+      <c r="H94" s="5" t="s">
         <v>670</v>
       </c>
       <c r="I94" s="4" t="s">
@@ -5498,7 +5520,7 @@
       <c r="A95" s="3">
         <v>93</v>
       </c>
-      <c r="B95" s="4" t="s">
+      <c r="B95" s="5" t="s">
         <v>93</v>
       </c>
       <c r="C95" s="4" t="s">
@@ -5516,7 +5538,7 @@
       <c r="G95" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="H95" s="4" t="s">
+      <c r="H95" s="5" t="s">
         <v>671</v>
       </c>
       <c r="I95" s="4" t="s">
@@ -5527,7 +5549,7 @@
       <c r="A96" s="3">
         <v>94</v>
       </c>
-      <c r="B96" s="4" t="s">
+      <c r="B96" s="5" t="s">
         <v>94</v>
       </c>
       <c r="C96" s="4" t="s">
@@ -5545,7 +5567,7 @@
       <c r="G96" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="H96" s="4" t="s">
+      <c r="H96" s="5" t="s">
         <v>672</v>
       </c>
       <c r="I96" s="4" t="s">
@@ -5556,7 +5578,7 @@
       <c r="A97" s="3">
         <v>95</v>
       </c>
-      <c r="B97" s="4" t="s">
+      <c r="B97" s="5" t="s">
         <v>95</v>
       </c>
       <c r="C97" s="4" t="s">
@@ -5574,7 +5596,7 @@
       <c r="G97" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="H97" s="4" t="s">
+      <c r="H97" s="5" t="s">
         <v>673</v>
       </c>
       <c r="I97" s="4" t="s">
@@ -5585,7 +5607,7 @@
       <c r="A98" s="3">
         <v>96</v>
       </c>
-      <c r="B98" s="4" t="s">
+      <c r="B98" s="5" t="s">
         <v>96</v>
       </c>
       <c r="C98" s="4" t="s">
@@ -5603,7 +5625,7 @@
       <c r="G98" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="H98" s="4" t="s">
+      <c r="H98" s="5" t="s">
         <v>674</v>
       </c>
       <c r="I98" s="4" t="s">
@@ -5614,7 +5636,7 @@
       <c r="A99" s="3">
         <v>97</v>
       </c>
-      <c r="B99" s="4" t="s">
+      <c r="B99" s="5" t="s">
         <v>97</v>
       </c>
       <c r="C99" s="4" t="s">
@@ -5632,7 +5654,7 @@
       <c r="G99" s="4" t="s">
         <v>483</v>
       </c>
-      <c r="H99" s="4" t="s">
+      <c r="H99" s="5" t="s">
         <v>675</v>
       </c>
       <c r="I99" s="4" t="s">
@@ -5643,7 +5665,7 @@
       <c r="A100" s="3">
         <v>98</v>
       </c>
-      <c r="B100" s="4" t="s">
+      <c r="B100" s="5" t="s">
         <v>98</v>
       </c>
       <c r="C100" s="4" t="s">
@@ -5661,7 +5683,7 @@
       <c r="G100" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="H100" s="4" t="s">
+      <c r="H100" s="5" t="s">
         <v>781</v>
       </c>
       <c r="I100" s="4" t="s">
@@ -5672,7 +5694,7 @@
       <c r="A101" s="3">
         <v>99</v>
       </c>
-      <c r="B101" s="4" t="s">
+      <c r="B101" s="5" t="s">
         <v>99</v>
       </c>
       <c r="C101" s="4" t="s">
@@ -5690,7 +5712,7 @@
       <c r="G101" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="H101" s="4" t="s">
+      <c r="H101" s="5" t="s">
         <v>782</v>
       </c>
       <c r="I101" s="4" t="s">
@@ -5701,7 +5723,7 @@
       <c r="A102" s="3">
         <v>100</v>
       </c>
-      <c r="B102" s="4" t="s">
+      <c r="B102" s="5" t="s">
         <v>100</v>
       </c>
       <c r="C102" s="4" t="s">
@@ -5719,12 +5741,15 @@
       <c r="G102" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="H102" s="4" t="s">
+      <c r="H102" s="5" t="s">
         <v>783</v>
       </c>
       <c r="I102" s="4" t="s">
         <v>785</v>
       </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H103" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
